--- a/leads-report-20260709-104204.xlsx
+++ b/leads-report-20260709-104204.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="643" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="152">
   <si>
     <t>ID</t>
   </si>
@@ -466,6 +466,15 @@
   </si>
   <si>
     <t xml:space="preserve">Pansen Engineering </t>
+  </si>
+  <si>
+    <t>costing accepted or rejected</t>
+  </si>
+  <si>
+    <t>Costing completion date</t>
+  </si>
+  <si>
+    <t>Costing accepted date</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G160"/>
+  <dimension ref="A1:J160"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
@@ -1283,9 +1292,12 @@
     <col min="5" max="5" width="26.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1307,8 +1319,17 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>10</v>
       </c>
@@ -1328,7 +1349,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>13</v>
       </c>
@@ -1351,7 +1372,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>14</v>
       </c>
@@ -1374,7 +1395,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>15</v>
       </c>
@@ -1397,7 +1418,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>16</v>
       </c>
@@ -1420,7 +1441,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>17</v>
       </c>
@@ -1443,7 +1464,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>18</v>
       </c>
@@ -1466,7 +1487,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>19</v>
       </c>
@@ -1486,7 +1507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>20</v>
       </c>
@@ -1509,7 +1530,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>22</v>
       </c>
@@ -1532,7 +1553,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>23</v>
       </c>
@@ -1552,7 +1573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>24</v>
       </c>
@@ -1575,7 +1596,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>26</v>
       </c>
@@ -1598,7 +1619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>27</v>
       </c>
@@ -1621,7 +1642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>28</v>
       </c>
